--- a/input_files/StrachanCollection_raw.xlsx
+++ b/input_files/StrachanCollection_raw.xlsx
@@ -1,43 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Q:\SAC\Collections\ArchivesAndArchiveRoom\Strachan Collection\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D7499894-B98A-482C-86FE-6A86BB72ED24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{990973F4-3EED-4CFF-8BBB-32241EFDBC84}"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="392">
   <si>
     <t>Primary Call No Desc</t>
   </si>
@@ -156,7 +130,7 @@
     <t>Les Marionettes.</t>
   </si>
   <si>
-    <t>Paris, G. Visat.</t>
+    <t>Paris, G.Visat.</t>
   </si>
   <si>
     <t>40 x 33.5cm</t>
@@ -177,7 +151,7 @@
     <t>Saisons.</t>
   </si>
   <si>
-    <t>Paris, R. Blanchet.</t>
+    <t>Paris, R.Blanchet.</t>
   </si>
   <si>
     <t>40 x 17cm</t>
@@ -198,7 +172,7 @@
     <t>circa 1970</t>
   </si>
   <si>
-    <t>New York and Paris, M. Sautier</t>
+    <t>New York and Paris, M.Sautier</t>
   </si>
   <si>
     <t>50 x 33cm</t>
@@ -420,7 +394,7 @@
     <t>Orénoque.</t>
   </si>
   <si>
-    <t>Paris, Librairie A. Blaizot. Text printed by Durand, etchings by Lacourière.</t>
+    <t>Paris, Librairie A.Blaizot. Text printed by Durand, etchings by Lacourière.</t>
   </si>
   <si>
     <t>49 x 37cm</t>
@@ -438,7 +412,7 @@
     <t>Fautrier l'enragé.</t>
   </si>
   <si>
-    <t>Paris, A. Blaizot.</t>
+    <t>Paris, A.Blaizot.</t>
   </si>
   <si>
     <t>49 x 38cm</t>
@@ -606,7 +580,7 @@
     <t>Regards sur le passé.</t>
   </si>
   <si>
-    <t>Paris, P. Belfond. Printed by Fequet &amp; Baudier.</t>
+    <t>Paris, P.Belfond. Printed by Fequet &amp; Baudier.</t>
   </si>
   <si>
     <t>Includes 3 engravings</t>
@@ -771,27 +745,7 @@
     <t>STRACHAN.173</t>
   </si>
   <si>
-    <r>
-      <t>Marchand, Andr</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>é</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Andale WT"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
+    <t>Marchand, André.</t>
   </si>
   <si>
     <t>Gide, André.</t>
@@ -812,9 +766,6 @@
     <t>STRACHAN.174</t>
   </si>
   <si>
-    <t>Marchand, André.</t>
-  </si>
-  <si>
     <t>Perse, Saint-John.</t>
   </si>
   <si>
@@ -965,27 +916,7 @@
     <t>STRACHAN.194</t>
   </si>
   <si>
-    <r>
-      <t>Caraire, Andr</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>é</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Andale WT"/>
-        <family val="2"/>
-      </rPr>
-      <t>e.</t>
-    </r>
+    <t>Caraire, Andrée.</t>
   </si>
   <si>
     <t>Telle la feuille et l'arbre.</t>
@@ -1000,27 +931,7 @@
     <t>STRACHAN.195</t>
   </si>
   <si>
-    <r>
-      <t>Pr</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>é</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Andale WT"/>
-        <family val="2"/>
-      </rPr>
-      <t>vert, Jacques.</t>
-    </r>
+    <t>Prévert, Jacques.</t>
   </si>
   <si>
     <t>Le Jour des temps.</t>
@@ -1077,27 +988,7 @@
     <t>Picasso, Pablo, 1881-1973.</t>
   </si>
   <si>
-    <r>
-      <t>Balzac, Honor</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>é</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Andale WT"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> de.</t>
-    </r>
+    <t>Balzac, Honoré de.</t>
   </si>
   <si>
     <t>Le Chef-d'ouevre inconnu.</t>
@@ -1193,27 +1084,7 @@
     <t>STRACHAN.228</t>
   </si>
   <si>
-    <r>
-      <t>Survage, L</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>é</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Andale WT"/>
-        <family val="2"/>
-      </rPr>
-      <t>opold.</t>
-    </r>
+    <t>Survage, Léopold.</t>
   </si>
   <si>
     <t>Pégase.</t>
@@ -1234,27 +1105,7 @@
     <t>Vasarely, Victor.</t>
   </si>
   <si>
-    <r>
-      <t>Descartes, Ren</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>é</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Andale WT"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
+    <t>Descartes, René.</t>
   </si>
   <si>
     <t>Discours sur la méthode.</t>
@@ -1341,45 +1192,27 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="#0"/>
-  </numFmts>
-  <fonts count="6">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <sz val="8"/>
-      <color theme="1"/>
-      <name val="Andale WT"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color theme="1"/>
       <name val="Andale WT"/>
     </font>
     <font>
       <sz val="8"/>
-      <color theme="1"/>
       <name val="Tahoma"/>
-      <family val="2"/>
     </font>
     <font>
+      <color rgb="FF333333"/>
       <sz val="8"/>
-      <color rgb="FF333333"/>
       <name val=" Andale WT"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1396,6 +1229,19 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF608BB4"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF608BB4"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF608BB4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1450,351 +1296,51 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF608BB4"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF608BB4"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FF608BB4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="16">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Tahoma"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Andale WT"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="medium">
-          <color rgb="FF608BB4"/>
-        </left>
-        <right style="medium">
-          <color rgb="FF608BB4"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Tahoma"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Tahoma"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Tahoma"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Tahoma"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Tahoma"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Andale WT"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="medium">
-          <color rgb="FFCCCCCC"/>
-        </left>
-        <right style="medium">
-          <color rgb="FFCCCCCC"/>
-        </right>
-        <top style="medium">
-          <color rgb="FFCCCCCC"/>
-        </top>
-        <bottom style="medium">
-          <color rgb="FFCCCCCC"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="medium">
-          <color rgb="FF608BB4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="medium">
-          <color rgb="FF608BB4"/>
-        </top>
-      </border>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1805,27 +1351,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{71224DE9-5FE6-40D9-8FD0-4C286D99A913}" name="Table1" displayName="Table1" ref="A1:L59" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0" headerRowBorderDxfId="14" tableBorderDxfId="15">
-  <autoFilter ref="A1:L59" xr:uid="{71224DE9-5FE6-40D9-8FD0-4C286D99A913}"/>
-  <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{EDBACF7D-BC82-4DAC-ADB4-E1D7DA068894}" name="Primary Call No Desc" dataDxfId="13"/>
-    <tableColumn id="2" xr3:uid="{FC755583-655B-418A-B67F-2A9E814B7DCC}" name="Artist" dataDxfId="12"/>
-    <tableColumn id="3" xr3:uid="{B316BB7F-483E-4632-B3D4-0EA7B4989195}" name="Author of Text" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{9DF9F811-A9CB-48C3-8F42-674EDC842B2A}" name="Author" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{0ED5F599-09AB-49D6-B144-AD2DEF2429E3}" name="Title" dataDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{FFFF88C1-703F-434F-B7F5-F14F8890B480}" name="Publication date" dataDxfId="8"/>
-    <tableColumn id="7" xr3:uid="{F5BF91A8-EB5D-4F4F-AAEF-603965560D17}" name="Publisher" dataDxfId="7"/>
-    <tableColumn id="8" xr3:uid="{0D1671F3-3D37-471C-884B-600DB6A9E8A8}" name="Subtitle" dataDxfId="6"/>
-    <tableColumn id="9" xr3:uid="{F9E53F40-CE7C-4C03-B112-298512C21CB8}" name="Pagination" dataDxfId="5"/>
-    <tableColumn id="10" xr3:uid="{7E8968B0-94D7-41E3-A336-A1BD70EAE369}" name="Size (cm)" dataDxfId="4"/>
-    <tableColumn id="11" xr3:uid="{53AF4F70-9D9B-4EA4-B2BB-E06341D6C128}" name="Complete?" dataDxfId="3"/>
-    <tableColumn id="12" xr3:uid="{2DDC3FDD-453F-4217-B8AA-2C72055DFFB6}" name="Supplementary info" dataDxfId="2"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight13" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1839,44 +1364,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -1904,31 +1429,14 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -1956,23 +1464,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1984,165 +1475,224 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
+                <a:tint val="100000"/>
                 <a:shade val="100000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FD2678D-CEF5-4C83-9059-A1E2D70C4631}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L59"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="14" style="2" customWidth="1"/>
-    <col min="2" max="2" width="27.7109375" style="2" customWidth="1"/>
-    <col min="3" max="3" width="40.140625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="26.85546875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="32.42578125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" style="2" customWidth="1"/>
-    <col min="7" max="7" width="23" style="2" customWidth="1"/>
-    <col min="8" max="8" width="18.42578125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="7.28515625" style="2" customWidth="1"/>
-    <col min="10" max="11" width="11" style="2" customWidth="1"/>
-    <col min="12" max="12" width="36.5703125" style="2" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="27.714285714285715" customWidth="1"/>
+    <col min="3" max="3" width="40.142857142857146" customWidth="1"/>
+    <col min="4" max="4" width="26.857142857142858" customWidth="1"/>
+    <col min="5" max="5" width="32.42857142857143" customWidth="1"/>
+    <col min="6" max="6" width="10.714285714285714" customWidth="1"/>
+    <col min="7" max="7" width="23" customWidth="1"/>
+    <col min="8" max="8" width="18.428571428571427" customWidth="1"/>
+    <col min="9" max="9" width="9.285714285714286" customWidth="1"/>
+    <col min="10" max="11" width="11" customWidth="1"/>
+    <col min="12" max="12" width="36.57142857142857" customWidth="1"/>
+    <col min="13" max="24" width="13.571428571428571" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="26.25" customHeight="1" thickBot="1">
+    <row r="1" ht="26.25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2180,2135 +1730,2098 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="15.75" thickBot="1">
-      <c r="A2" s="3" t="s">
+    <row r="2" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="5">
+      <c r="F2" s="3">
         <v>1961</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6">
+      <c r="H2" s="4"/>
+      <c r="I2" s="4">
         <v>3</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="J2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="K2" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="L2" s="9" t="s">
+      <c r="K2" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2" s="7" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="15.75" thickBot="1">
-      <c r="A3" s="4" t="s">
+    <row r="3" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F3" s="10">
+      <c r="F3" s="8">
         <v>1971</v>
       </c>
-      <c r="G3" s="11" t="s">
+      <c r="G3" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6">
+      <c r="H3" s="4"/>
+      <c r="I3" s="4">
         <v>40</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="K3" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="L3" s="6" t="s">
+      <c r="K3" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L3" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="23.25" thickBot="1">
-      <c r="A4" s="4" t="s">
+    <row r="4" ht="23.25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="12">
+      <c r="F4" s="10">
         <v>1967</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H4" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="I4" s="6">
+      <c r="I4" s="4">
         <v>20</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="J4" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="K4" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="L4" s="9" t="s">
+      <c r="K4" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L4" s="7" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="23.25" thickBot="1">
-      <c r="A5" s="4" t="s">
+    <row r="5" ht="23.25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F5" s="12">
+      <c r="F5" s="10">
         <v>1970</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6">
+      <c r="H5" s="4"/>
+      <c r="I5" s="4">
         <v>8</v>
       </c>
-      <c r="J5" s="7" t="s">
+      <c r="J5" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="K5" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="L5" s="9" t="s">
+      <c r="K5" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L5" s="7" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="23.25" thickBot="1">
-      <c r="A6" s="4" t="s">
+    <row r="6" ht="23.25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="F6" s="12">
+      <c r="F6" s="10">
         <v>1972</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6">
+      <c r="H6" s="4"/>
+      <c r="I6" s="4">
         <v>17</v>
       </c>
-      <c r="J6" s="7" t="s">
+      <c r="J6" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="K6" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="L6" s="9" t="s">
+      <c r="K6" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L6" s="7" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="15.75" thickBot="1">
-      <c r="A7" s="4" t="s">
+    <row r="7" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="F7" s="12" t="s">
+      <c r="F7" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6">
+      <c r="H7" s="4"/>
+      <c r="I7" s="4">
         <v>7</v>
       </c>
-      <c r="J7" s="7" t="s">
+      <c r="J7" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="K7" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="L7" s="7" t="s">
+      <c r="K7" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L7" s="5" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="15.75" thickBot="1">
-      <c r="A8" s="4" t="s">
+    <row r="8" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="10">
         <v>1975</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6">
+      <c r="H8" s="4"/>
+      <c r="I8" s="4">
         <v>21</v>
       </c>
-      <c r="J8" s="7" t="s">
+      <c r="J8" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="K8" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="L8" s="6" t="s">
+      <c r="K8" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L8" s="4" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="34.5" thickBot="1">
-      <c r="A9" s="4" t="s">
+    <row r="9" ht="34.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="F9" s="12">
+      <c r="F9" s="10">
         <v>1962</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="G9" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6">
+      <c r="H9" s="4"/>
+      <c r="I9" s="4">
         <v>8</v>
       </c>
-      <c r="J9" s="7" t="s">
+      <c r="J9" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="K9" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="L9" s="9" t="s">
+      <c r="K9" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L9" s="7" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="23.25" thickBot="1">
-      <c r="A10" s="4" t="s">
+    <row r="10" ht="23.25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="F10" s="12">
+      <c r="F10" s="10">
         <v>1973</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G10" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="H10" s="7" t="s">
+      <c r="H10" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="I10" s="6">
-        <v>18</v>
-      </c>
-      <c r="J10" s="7" t="s">
+      <c r="I10" s="4">
+        <v>18</v>
+      </c>
+      <c r="J10" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="K10" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="L10" s="9" t="s">
+      <c r="K10" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L10" s="7" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="15.75" thickBot="1">
-      <c r="A11" s="4" t="s">
+    <row r="11" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="F11" s="12">
+      <c r="F11" s="10">
         <v>1957</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="G11" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6">
+      <c r="H11" s="4"/>
+      <c r="I11" s="4">
         <v>2</v>
       </c>
-      <c r="J11" s="7" t="s">
+      <c r="J11" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="K11" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="L11" s="7" t="s">
+      <c r="K11" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L11" s="5" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="57" thickBot="1">
-      <c r="A12" s="4" t="s">
+    <row r="12" ht="57" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="F12" s="12">
+      <c r="F12" s="10">
         <v>1948</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="G12" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6">
+      <c r="H12" s="4"/>
+      <c r="I12" s="4">
         <v>40</v>
       </c>
-      <c r="J12" s="7" t="s">
+      <c r="J12" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="K12" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="L12" s="9" t="s">
+      <c r="K12" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L12" s="7" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="15.75" thickBot="1">
-      <c r="A13" s="4" t="s">
+    <row r="13" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="F13" s="12">
+      <c r="F13" s="10">
         <v>1966</v>
       </c>
-      <c r="G13" s="4" t="s">
+      <c r="G13" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6">
+      <c r="H13" s="4"/>
+      <c r="I13" s="4">
         <v>11</v>
       </c>
-      <c r="J13" s="7" t="s">
+      <c r="J13" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="K13" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="L13" s="7" t="s">
+      <c r="K13" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L13" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="15.75" thickBot="1">
-      <c r="A14" s="4" t="s">
+    <row r="14" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="F14" s="12">
+      <c r="F14" s="10">
         <v>1951</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G14" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6">
+      <c r="H14" s="4"/>
+      <c r="I14" s="4">
         <v>22</v>
       </c>
-      <c r="J14" s="7" t="s">
+      <c r="J14" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="K14" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="L14" s="13" t="s">
+      <c r="K14" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L14" s="11" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="15.75" thickBot="1">
-      <c r="A15" s="4" t="s">
+    <row r="15" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="F15" s="12">
+      <c r="F15" s="10">
         <v>1965</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="G15" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6">
-        <v>18</v>
-      </c>
-      <c r="J15" s="7" t="s">
+      <c r="H15" s="4"/>
+      <c r="I15" s="4">
+        <v>18</v>
+      </c>
+      <c r="J15" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="K15" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="L15" s="7" t="s">
+      <c r="K15" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L15" s="5" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="15.75" thickBot="1">
-      <c r="A16" s="14" t="s">
+    <row r="16" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="B16" s="14" t="s">
+      <c r="B16" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="C16" s="14" t="s">
+      <c r="C16" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="D16" s="15" t="s">
+      <c r="D16" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="F16" s="12">
+      <c r="F16" s="10">
         <v>1968</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="G16" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6">
+      <c r="H16" s="4"/>
+      <c r="I16" s="4">
         <v>8</v>
       </c>
-      <c r="J16" s="7" t="s">
+      <c r="J16" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="K16" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="L16" s="6" t="s">
+      <c r="K16" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L16" s="4" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="23.25" thickBot="1">
-      <c r="A17" s="4" t="s">
+    <row r="17" ht="23.25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="E17" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="F17" s="12">
+      <c r="F17" s="10">
         <v>1942</v>
       </c>
-      <c r="G17" s="4" t="s">
+      <c r="G17" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="H17" s="6"/>
-      <c r="I17" s="6">
+      <c r="H17" s="4"/>
+      <c r="I17" s="4">
         <v>1</v>
       </c>
-      <c r="J17" s="7" t="s">
+      <c r="J17" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="K17" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="L17" s="9" t="s">
+      <c r="K17" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L17" s="7" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="23.25" thickBot="1">
-      <c r="A18" s="4" t="s">
+    <row r="18" ht="23.25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="E18" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="F18" s="12">
+      <c r="F18" s="10">
         <v>1949</v>
       </c>
-      <c r="G18" s="4" t="s">
+      <c r="G18" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6">
+      <c r="H18" s="4"/>
+      <c r="I18" s="4">
         <v>4</v>
       </c>
-      <c r="J18" s="7" t="s">
+      <c r="J18" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="K18" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="L18" s="9" t="s">
+      <c r="K18" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L18" s="7" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="23.25" thickBot="1">
-      <c r="A19" s="4" t="s">
+    <row r="19" ht="23.25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="E19" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="F19" s="12">
+      <c r="F19" s="10">
         <v>1965</v>
       </c>
-      <c r="G19" s="4" t="s">
+      <c r="G19" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="H19" s="6"/>
-      <c r="I19" s="6">
+      <c r="H19" s="4"/>
+      <c r="I19" s="4">
         <v>20</v>
       </c>
-      <c r="J19" s="7" t="s">
+      <c r="J19" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="K19" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="L19" s="9" t="s">
+      <c r="K19" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L19" s="7" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="15.75" thickBot="1">
-      <c r="A20" s="4" t="s">
+    <row r="20" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="E20" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="F20" s="12">
+      <c r="F20" s="10">
         <v>1964</v>
       </c>
-      <c r="G20" s="4" t="s">
+      <c r="G20" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="H20" s="6"/>
-      <c r="I20" s="6">
+      <c r="H20" s="4"/>
+      <c r="I20" s="4">
         <v>8</v>
       </c>
-      <c r="J20" s="7" t="s">
+      <c r="J20" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="K20" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="L20" s="9" t="s">
+      <c r="K20" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L20" s="7" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="15.75" thickBot="1">
-      <c r="A21" s="4" t="s">
+    <row r="21" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="E21" s="4" t="s">
+      <c r="E21" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="F21" s="12">
+      <c r="F21" s="10">
         <v>1955</v>
       </c>
-      <c r="G21" s="4" t="s">
+      <c r="G21" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="H21" s="6"/>
-      <c r="I21" s="6">
+      <c r="H21" s="4"/>
+      <c r="I21" s="4">
         <v>8</v>
       </c>
-      <c r="J21" s="7" t="s">
+      <c r="J21" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="K21" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="L21" s="7" t="s">
+      <c r="K21" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L21" s="5" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="23.25" thickBot="1">
-      <c r="A22" s="4" t="s">
+    <row r="22" ht="23.25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="E22" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="F22" s="4">
+      <c r="F22" s="2">
         <v>1968</v>
       </c>
-      <c r="G22" s="4" t="s">
+      <c r="G22" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6">
+      <c r="H22" s="4"/>
+      <c r="I22" s="4">
         <v>24</v>
       </c>
-      <c r="J22" s="15" t="s">
+      <c r="J22" s="13" t="s">
         <v>164</v>
       </c>
-      <c r="K22" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="L22" s="9" t="s">
+      <c r="K22" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L22" s="7" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="23.25" thickBot="1">
-      <c r="A23" s="6" t="s">
+    <row r="23" ht="23.25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="C23" s="14" t="s">
+      <c r="C23" s="12" t="s">
         <v>168</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="E23" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="F23" s="12">
+      <c r="F23" s="10">
         <v>1961</v>
       </c>
-      <c r="G23" s="4" t="s">
+      <c r="G23" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="H23" s="6"/>
-      <c r="I23" s="6">
+      <c r="H23" s="4"/>
+      <c r="I23" s="4">
         <v>20</v>
       </c>
-      <c r="J23" s="7" t="s">
+      <c r="J23" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="K23" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="L23" s="9" t="s">
+      <c r="K23" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L23" s="7" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="15.75" thickBot="1">
-      <c r="A24" s="6" t="s">
+    <row r="24" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="C24" s="14" t="s">
+      <c r="C24" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="E24" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="F24" s="12">
+      <c r="F24" s="10">
         <v>1965</v>
       </c>
-      <c r="G24" s="4" t="s">
+      <c r="G24" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="H24" s="6"/>
-      <c r="I24" s="6">
+      <c r="H24" s="4"/>
+      <c r="I24" s="4">
         <v>12</v>
       </c>
-      <c r="J24" s="7" t="s">
+      <c r="J24" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="K24" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="L24" s="6" t="s">
+      <c r="K24" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L24" s="4" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="15.75" thickBot="1">
-      <c r="A25" s="4" t="s">
+    <row r="25" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C25" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D25" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="E25" s="4" t="s">
+      <c r="E25" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="F25" s="4">
+      <c r="F25" s="2">
         <v>1968</v>
       </c>
-      <c r="G25" s="4" t="s">
+      <c r="G25" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="H25" s="6"/>
-      <c r="I25" s="6">
-        <v>18</v>
-      </c>
-      <c r="J25" s="6" t="s">
+      <c r="H25" s="4"/>
+      <c r="I25" s="4">
+        <v>18</v>
+      </c>
+      <c r="J25" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="K25" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="L25" s="8" t="s">
+      <c r="K25" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L25" s="6" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="15.75" thickBot="1">
-      <c r="A26" s="4" t="s">
+    <row r="26" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C26" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="D26" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="E26" s="4" t="s">
+      <c r="E26" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="F26" s="4">
+      <c r="F26" s="2">
         <v>1971</v>
       </c>
-      <c r="G26" s="4" t="s">
+      <c r="G26" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="H26" s="6"/>
-      <c r="I26" s="6">
+      <c r="H26" s="4"/>
+      <c r="I26" s="4">
         <v>16</v>
       </c>
-      <c r="J26" s="6" t="s">
+      <c r="J26" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="K26" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="L26" s="8" t="s">
+      <c r="K26" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L26" s="6" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="23.25" thickBot="1">
-      <c r="A27" s="4" t="s">
+    <row r="27" ht="23.25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="C27" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="D27" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="E27" s="4" t="s">
+      <c r="E27" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="F27" s="4">
+      <c r="F27" s="2">
         <v>1965</v>
       </c>
-      <c r="G27" s="4" t="s">
+      <c r="G27" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="H27" s="6"/>
-      <c r="I27" s="6">
+      <c r="H27" s="4"/>
+      <c r="I27" s="4">
         <v>10</v>
       </c>
-      <c r="J27" s="6" t="s">
+      <c r="J27" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="K27" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="L27" s="8" t="s">
+      <c r="K27" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L27" s="6" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="15.75" thickBot="1">
-      <c r="A28" s="14" t="s">
+    <row r="28" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A28" s="12" t="s">
         <v>198</v>
       </c>
-      <c r="B28" s="14" t="s">
+      <c r="B28" s="12" t="s">
         <v>199</v>
       </c>
-      <c r="C28" s="14" t="s">
+      <c r="C28" s="12" t="s">
         <v>168</v>
       </c>
-      <c r="D28" s="14" t="s">
+      <c r="D28" s="12" t="s">
         <v>199</v>
       </c>
-      <c r="E28" s="6" t="s">
+      <c r="E28" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="F28" s="6">
+      <c r="F28" s="4">
         <v>1959</v>
       </c>
-      <c r="G28" s="6" t="s">
+      <c r="G28" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="H28" s="6"/>
-      <c r="I28" s="6">
+      <c r="H28" s="4"/>
+      <c r="I28" s="4">
         <v>20</v>
       </c>
-      <c r="J28" s="6" t="s">
+      <c r="J28" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="K28" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="L28" s="8" t="s">
+      <c r="K28" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L28" s="6" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="33.75" thickBot="1">
-      <c r="A29" s="4" t="s">
+    <row r="29" ht="33.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B29" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="C29" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="D29" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="E29" s="4" t="s">
+      <c r="E29" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="F29" s="4">
+      <c r="F29" s="2">
         <v>1951</v>
       </c>
-      <c r="G29" s="4" t="s">
+      <c r="G29" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="H29" s="6"/>
-      <c r="I29" s="6">
+      <c r="H29" s="4"/>
+      <c r="I29" s="4">
         <v>17</v>
       </c>
-      <c r="J29" s="6" t="s">
+      <c r="J29" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="K29" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="L29" s="8" t="s">
+      <c r="K29" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L29" s="6" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="15.75" thickBot="1">
-      <c r="A30" s="14" t="s">
+    <row r="30" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A30" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B30" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="C30" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="D30" s="6" t="s">
+      <c r="D30" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="E30" s="6" t="s">
+      <c r="E30" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="F30" s="6">
+      <c r="F30" s="4">
         <v>1955</v>
       </c>
-      <c r="G30" s="6" t="s">
+      <c r="G30" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="H30" s="6"/>
-      <c r="I30" s="6">
+      <c r="H30" s="4"/>
+      <c r="I30" s="4">
         <v>4</v>
       </c>
-      <c r="J30" s="6" t="s">
+      <c r="J30" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="K30" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="L30" s="6" t="s">
+      <c r="K30" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L30" s="4" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="15.75" thickBot="1">
-      <c r="A31" s="4" t="s">
+    <row r="31" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="B31" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="C31" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="D31" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="E31" s="4" t="s">
+      <c r="E31" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="F31" s="4">
+      <c r="F31" s="2">
         <v>1977</v>
       </c>
-      <c r="G31" s="4" t="s">
+      <c r="G31" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="H31" s="6"/>
-      <c r="I31" s="6">
+      <c r="H31" s="4"/>
+      <c r="I31" s="4">
         <v>16</v>
       </c>
-      <c r="J31" s="6" t="s">
+      <c r="J31" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="K31" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="L31" s="8" t="s">
+      <c r="K31" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L31" s="6" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="15.75" thickBot="1">
-      <c r="A32" s="4" t="s">
+    <row r="32" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="B32" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="C32" s="4" t="s">
+      <c r="C32" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="D32" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="E32" s="4" t="s">
+      <c r="E32" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="F32" s="4">
+      <c r="F32" s="2">
         <v>1975</v>
       </c>
-      <c r="G32" s="4" t="s">
+      <c r="G32" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="H32" s="6"/>
-      <c r="I32" s="6">
+      <c r="H32" s="4"/>
+      <c r="I32" s="4">
         <v>24</v>
       </c>
-      <c r="J32" s="6" t="s">
+      <c r="J32" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="K32" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="L32" s="8" t="s">
+      <c r="K32" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L32" s="6" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="23.25" thickBot="1">
-      <c r="A33" s="4" t="s">
+    <row r="33" ht="23.25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="B33" s="4" t="s">
+      <c r="B33" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="C33" s="14" t="s">
+      <c r="C33" s="12" t="s">
         <v>232</v>
       </c>
-      <c r="D33" s="6" t="s">
+      <c r="D33" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="E33" s="6" t="s">
+      <c r="E33" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="F33" s="6">
+      <c r="F33" s="4">
         <v>1958</v>
       </c>
-      <c r="G33" s="6" t="s">
+      <c r="G33" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="H33" s="6"/>
-      <c r="I33" s="6">
+      <c r="H33" s="4"/>
+      <c r="I33" s="4">
         <v>14</v>
       </c>
-      <c r="J33" s="6" t="s">
+      <c r="J33" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="K33" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="L33" s="8" t="s">
+      <c r="K33" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L33" s="6" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="15.75" thickBot="1">
-      <c r="A34" s="4" t="s">
+    <row r="34" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="B34" s="4" t="s">
+      <c r="B34" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="C34" s="14" t="s">
+      <c r="C34" s="12" t="s">
         <v>238</v>
       </c>
-      <c r="D34" s="6" t="s">
+      <c r="D34" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="E34" s="6" t="s">
+      <c r="E34" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="F34" s="6">
+      <c r="F34" s="4">
         <v>1964</v>
       </c>
-      <c r="G34" s="6" t="s">
+      <c r="G34" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="H34" s="6"/>
-      <c r="I34" s="6">
+      <c r="H34" s="4"/>
+      <c r="I34" s="4">
         <v>6</v>
       </c>
-      <c r="J34" s="6" t="s">
+      <c r="J34" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="K34" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="L34" s="6" t="s">
+      <c r="K34" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L34" s="4" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="23.25" thickBot="1">
-      <c r="A35" s="4" t="s">
+    <row r="35" ht="23.25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="B35" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="C35" s="4" t="s">
+      <c r="C35" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="D35" s="4" t="s">
+      <c r="D35" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="E35" s="4" t="s">
+      <c r="E35" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="F35" s="4">
+      <c r="F35" s="2">
         <v>1948</v>
       </c>
-      <c r="G35" s="4" t="s">
+      <c r="G35" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="H35" s="6"/>
-      <c r="I35" s="6">
+      <c r="H35" s="4"/>
+      <c r="I35" s="4">
         <v>8</v>
       </c>
-      <c r="J35" s="6" t="s">
+      <c r="J35" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="K35" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="L35" s="8" t="s">
+      <c r="K35" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L35" s="6" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="15.75" thickBot="1">
-      <c r="A36" s="4" t="s">
+    <row r="36" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="B36" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C36" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="C36" s="4" t="s">
+      <c r="D36" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="E36" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="D36" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="E36" s="4" t="s">
+      <c r="F36" s="2">
+        <v>1962</v>
+      </c>
+      <c r="G36" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="F36" s="4">
+      <c r="H36" s="4"/>
+      <c r="I36" s="4">
+        <v>59</v>
+      </c>
+      <c r="J36" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="K36" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L36" s="4" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="37" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="F37" s="2">
+        <v>1963</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="H37" s="4"/>
+      <c r="I37" s="4">
+        <v>12</v>
+      </c>
+      <c r="J37" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="K37" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L37" s="4"/>
+    </row>
+    <row r="38" ht="23.25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="C38" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="D38" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="F38" s="4">
+        <v>1976</v>
+      </c>
+      <c r="G38" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4">
+        <v>10</v>
+      </c>
+      <c r="J38" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="K38" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L38" s="6" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="39" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="F39" s="2">
+        <v>1961</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="H39" s="4"/>
+      <c r="I39" s="4">
+        <v>32</v>
+      </c>
+      <c r="J39" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="K39" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L39" s="6" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="40" ht="23.25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="F40" s="4">
+        <v>1960</v>
+      </c>
+      <c r="G40" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4">
+        <v>62</v>
+      </c>
+      <c r="J40" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="K40" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L40" s="6" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A41" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="F41" s="4">
+        <v>1964</v>
+      </c>
+      <c r="G41" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4">
+        <v>48</v>
+      </c>
+      <c r="J41" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="K41" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L41" s="6" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="42" ht="23.25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A42" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="F42" s="4">
+        <v>1965</v>
+      </c>
+      <c r="G42" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="H42" s="4"/>
+      <c r="I42" s="4">
+        <v>42</v>
+      </c>
+      <c r="J42" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="K42" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L42" s="6" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="43" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="F43" s="2">
+        <v>1968</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="H43" s="4"/>
+      <c r="I43" s="4">
+        <v>26</v>
+      </c>
+      <c r="J43" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="K43" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L43" s="6" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="44" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="F44" s="2">
+        <v>1971</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="H44" s="4"/>
+      <c r="I44" s="4">
+        <v>22</v>
+      </c>
+      <c r="J44" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="K44" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L44" s="4" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="45" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="F45" s="2">
+        <v>1975</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="H45" s="4"/>
+      <c r="I45" s="4">
+        <v>20</v>
+      </c>
+      <c r="J45" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="K45" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L45" s="4" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="46" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="F46" s="2">
+        <v>1976</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="H46" s="4"/>
+      <c r="I46" s="4">
+        <v>28</v>
+      </c>
+      <c r="J46" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="K46" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L46" s="6" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="47" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="F47" s="2">
+        <v>1968</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="H47" s="4"/>
+      <c r="I47" s="4">
+        <v>16</v>
+      </c>
+      <c r="J47" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="K47" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L47" s="4" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="48" ht="33.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="F48" s="2">
+        <v>1931</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="H48" s="4"/>
+      <c r="I48" s="4">
+        <v>6</v>
+      </c>
+      <c r="J48" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="K48" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L48" s="6" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="49" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="F49" s="2">
+        <v>1948</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="H49" s="4"/>
+      <c r="I49" s="4">
+        <v>4</v>
+      </c>
+      <c r="J49" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="K49" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L49" s="4" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="50" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="F50" s="2">
+        <v>1967</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="H50" s="4"/>
+      <c r="I50" s="4">
+        <v>16</v>
+      </c>
+      <c r="J50" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="K50" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L50" s="6" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="51" ht="23.25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A51" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="F51" s="2">
+        <v>1964</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="H51" s="4"/>
+      <c r="I51" s="4">
+        <v>14</v>
+      </c>
+      <c r="J51" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="K51" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L51" s="6" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="52" ht="33.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="F52" s="2">
+        <v>1971</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="H52" s="4"/>
+      <c r="I52" s="4">
+        <v>22</v>
+      </c>
+      <c r="J52" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="K52" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L52" s="6" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="53" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A53" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="F53" s="2">
+        <v>1943</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="H53" s="4"/>
+      <c r="I53" s="4">
+        <v>4</v>
+      </c>
+      <c r="J53" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="K53" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L53" s="4" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="54" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="F54" s="2">
+        <v>1965</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="H54" s="4"/>
+      <c r="I54" s="4">
+        <v>28</v>
+      </c>
+      <c r="J54" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="K54" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L54" s="6" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="55" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A55" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="F55" s="2">
+        <v>1969</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="H55" s="4"/>
+      <c r="I55" s="4">
+        <v>6</v>
+      </c>
+      <c r="J55" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="K55" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L55" s="6" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="56" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A56" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="F56" s="2">
+        <v>1956</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="H56" s="4"/>
+      <c r="I56" s="4">
+        <v>8</v>
+      </c>
+      <c r="J56" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="K56" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L56" s="6" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="57" ht="23.25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A57" s="12" t="s">
+        <v>375</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="C57" s="12" t="s">
+        <v>377</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="E57" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="F57" s="4">
         <v>1962</v>
       </c>
-      <c r="G36" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="H36" s="6"/>
-      <c r="I36" s="6">
-        <v>59</v>
-      </c>
-      <c r="J36" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="K36" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="L36" s="6" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" ht="15.75" thickBot="1">
-      <c r="A37" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>258</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>259</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="E37" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="F37" s="4">
-        <v>1963</v>
-      </c>
-      <c r="G37" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="H37" s="6"/>
-      <c r="I37" s="6">
-        <v>12</v>
-      </c>
-      <c r="J37" s="6" t="s">
-        <v>263</v>
-      </c>
-      <c r="K37" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="L37" s="6"/>
-    </row>
-    <row r="38" spans="1:12" ht="23.25" thickBot="1">
-      <c r="A38" s="4" t="s">
-        <v>264</v>
-      </c>
-      <c r="B38" s="14" t="s">
-        <v>265</v>
-      </c>
-      <c r="C38" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="D38" s="14" t="s">
-        <v>265</v>
-      </c>
-      <c r="E38" s="6" t="s">
-        <v>266</v>
-      </c>
-      <c r="F38" s="6">
-        <v>1976</v>
-      </c>
-      <c r="G38" s="6" t="s">
-        <v>267</v>
-      </c>
-      <c r="H38" s="6"/>
-      <c r="I38" s="6">
+      <c r="G57" s="4" t="s">
+        <v>379</v>
+      </c>
+      <c r="H57" s="4"/>
+      <c r="I57" s="4">
+        <v>48</v>
+      </c>
+      <c r="J57" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="K57" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L57" s="6" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="58" ht="23.25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A58" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="C58" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="E58" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="F58" s="4">
+        <v>1971</v>
+      </c>
+      <c r="G58" s="4" t="s">
+        <v>384</v>
+      </c>
+      <c r="H58" s="4"/>
+      <c r="I58" s="4">
+        <v>42</v>
+      </c>
+      <c r="J58" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="K58" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L58" s="6" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="59" ht="33.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="D59" s="14" t="s">
+        <v>387</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="F59" s="2">
+        <v>1974</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="H59" s="4"/>
+      <c r="I59" s="4">
         <v>10</v>
       </c>
-      <c r="J38" s="6" t="s">
-        <v>268</v>
-      </c>
-      <c r="K38" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="L38" s="8" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" ht="15.75" thickBot="1">
-      <c r="A39" s="4" t="s">
-        <v>270</v>
-      </c>
-      <c r="B39" s="4" t="s">
-        <v>271</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>272</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>271</v>
-      </c>
-      <c r="E39" s="4" t="s">
-        <v>273</v>
-      </c>
-      <c r="F39" s="4">
-        <v>1961</v>
-      </c>
-      <c r="G39" s="4" t="s">
-        <v>274</v>
-      </c>
-      <c r="H39" s="6"/>
-      <c r="I39" s="6">
-        <v>32</v>
-      </c>
-      <c r="J39" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="K39" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="L39" s="8" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" ht="23.25" thickBot="1">
-      <c r="A40" s="4" t="s">
-        <v>276</v>
-      </c>
-      <c r="B40" s="4" t="s">
-        <v>277</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="D40" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="E40" s="6" t="s">
-        <v>279</v>
-      </c>
-      <c r="F40" s="6">
-        <v>1960</v>
-      </c>
-      <c r="G40" s="6" t="s">
-        <v>280</v>
-      </c>
-      <c r="H40" s="6"/>
-      <c r="I40" s="6">
-        <v>62</v>
-      </c>
-      <c r="J40" s="6" t="s">
-        <v>281</v>
-      </c>
-      <c r="K40" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="L40" s="8" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12">
-      <c r="A41" s="7" t="s">
-        <v>283</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="C41" s="6" t="s">
-        <v>284</v>
-      </c>
-      <c r="D41" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="E41" s="6" t="s">
-        <v>285</v>
-      </c>
-      <c r="F41" s="6">
-        <v>1964</v>
-      </c>
-      <c r="G41" s="6" t="s">
-        <v>286</v>
-      </c>
-      <c r="H41" s="6"/>
-      <c r="I41" s="6">
-        <v>48</v>
-      </c>
-      <c r="J41" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="K41" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="L41" s="8" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" ht="23.25" thickBot="1">
-      <c r="A42" s="7" t="s">
-        <v>288</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="C42" s="6" t="s">
-        <v>289</v>
-      </c>
-      <c r="D42" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="E42" s="6" t="s">
-        <v>290</v>
-      </c>
-      <c r="F42" s="6">
-        <v>1965</v>
-      </c>
-      <c r="G42" s="6" t="s">
-        <v>291</v>
-      </c>
-      <c r="H42" s="6"/>
-      <c r="I42" s="6">
-        <v>42</v>
-      </c>
-      <c r="J42" s="6" t="s">
-        <v>292</v>
-      </c>
-      <c r="K42" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="L42" s="8" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" ht="15.75" thickBot="1">
-      <c r="A43" s="4" t="s">
-        <v>294</v>
-      </c>
-      <c r="B43" s="4" t="s">
-        <v>295</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="D43" s="4" t="s">
-        <v>295</v>
-      </c>
-      <c r="E43" s="4" t="s">
-        <v>297</v>
-      </c>
-      <c r="F43" s="4">
-        <v>1968</v>
-      </c>
-      <c r="G43" s="4" t="s">
-        <v>298</v>
-      </c>
-      <c r="H43" s="6"/>
-      <c r="I43" s="6">
-        <v>26</v>
-      </c>
-      <c r="J43" s="6" t="s">
-        <v>299</v>
-      </c>
-      <c r="K43" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="L43" s="8" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" ht="15.75" thickBot="1">
-      <c r="A44" s="4" t="s">
-        <v>301</v>
-      </c>
-      <c r="B44" s="4" t="s">
-        <v>295</v>
-      </c>
-      <c r="C44" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="D44" s="4" t="s">
-        <v>295</v>
-      </c>
-      <c r="E44" s="4" t="s">
-        <v>303</v>
-      </c>
-      <c r="F44" s="4">
-        <v>1971</v>
-      </c>
-      <c r="G44" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="H44" s="6"/>
-      <c r="I44" s="6">
-        <v>22</v>
-      </c>
-      <c r="J44" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="K44" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="L44" s="6" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" ht="15.75" thickBot="1">
-      <c r="A45" s="4" t="s">
-        <v>306</v>
-      </c>
-      <c r="B45" s="4" t="s">
-        <v>295</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>307</v>
-      </c>
-      <c r="D45" s="4" t="s">
-        <v>295</v>
-      </c>
-      <c r="E45" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="F45" s="4">
-        <v>1975</v>
-      </c>
-      <c r="G45" s="4" t="s">
-        <v>309</v>
-      </c>
-      <c r="H45" s="6"/>
-      <c r="I45" s="6">
-        <v>20</v>
-      </c>
-      <c r="J45" s="6" t="s">
-        <v>292</v>
-      </c>
-      <c r="K45" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="L45" s="6" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" ht="15.75" thickBot="1">
-      <c r="A46" s="4" t="s">
-        <v>311</v>
-      </c>
-      <c r="B46" s="4" t="s">
-        <v>295</v>
-      </c>
-      <c r="C46" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="D46" s="4" t="s">
-        <v>295</v>
-      </c>
-      <c r="E46" s="4" t="s">
-        <v>313</v>
-      </c>
-      <c r="F46" s="4">
-        <v>1976</v>
-      </c>
-      <c r="G46" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="H46" s="6"/>
-      <c r="I46" s="6">
-        <v>28</v>
-      </c>
-      <c r="J46" s="6" t="s">
-        <v>315</v>
-      </c>
-      <c r="K46" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="L46" s="8" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" ht="15.75" thickBot="1">
-      <c r="A47" s="4" t="s">
-        <v>317</v>
-      </c>
-      <c r="B47" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="C47" s="4" t="s">
-        <v>319</v>
-      </c>
-      <c r="D47" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="E47" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="F47" s="4">
-        <v>1968</v>
-      </c>
-      <c r="G47" s="4" t="s">
-        <v>321</v>
-      </c>
-      <c r="H47" s="6"/>
-      <c r="I47" s="6">
-        <v>16</v>
-      </c>
-      <c r="J47" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="K47" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="L47" s="6" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" ht="33.75" thickBot="1">
-      <c r="A48" s="4" t="s">
-        <v>324</v>
-      </c>
-      <c r="B48" s="4" t="s">
-        <v>325</v>
-      </c>
-      <c r="C48" s="4" t="s">
-        <v>326</v>
-      </c>
-      <c r="D48" s="4" t="s">
-        <v>325</v>
-      </c>
-      <c r="E48" s="4" t="s">
-        <v>327</v>
-      </c>
-      <c r="F48" s="4">
-        <v>1931</v>
-      </c>
-      <c r="G48" s="4" t="s">
-        <v>328</v>
-      </c>
-      <c r="H48" s="6"/>
-      <c r="I48" s="6">
-        <v>6</v>
-      </c>
-      <c r="J48" s="6" t="s">
-        <v>329</v>
-      </c>
-      <c r="K48" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="L48" s="8" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12" ht="15.75" thickBot="1">
-      <c r="A49" s="4" t="s">
-        <v>331</v>
-      </c>
-      <c r="B49" s="4" t="s">
-        <v>325</v>
-      </c>
-      <c r="C49" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="D49" s="4" t="s">
-        <v>325</v>
-      </c>
-      <c r="E49" s="4" t="s">
-        <v>332</v>
-      </c>
-      <c r="F49" s="4">
-        <v>1948</v>
-      </c>
-      <c r="G49" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="H49" s="6"/>
-      <c r="I49" s="6">
-        <v>4</v>
-      </c>
-      <c r="J49" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="K49" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="L49" s="6" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12" ht="15.75" thickBot="1">
-      <c r="A50" s="4" t="s">
-        <v>334</v>
-      </c>
-      <c r="B50" s="4" t="s">
-        <v>335</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>336</v>
-      </c>
-      <c r="D50" s="4" t="s">
-        <v>335</v>
-      </c>
-      <c r="E50" s="4" t="s">
-        <v>337</v>
-      </c>
-      <c r="F50" s="4">
-        <v>1967</v>
-      </c>
-      <c r="G50" s="4" t="s">
-        <v>338</v>
-      </c>
-      <c r="H50" s="6"/>
-      <c r="I50" s="6">
-        <v>16</v>
-      </c>
-      <c r="J50" s="6" t="s">
-        <v>339</v>
-      </c>
-      <c r="K50" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="L50" s="8" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12" ht="23.25" thickBot="1">
-      <c r="A51" s="4" t="s">
-        <v>340</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>341</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>342</v>
-      </c>
-      <c r="D51" s="4" t="s">
-        <v>343</v>
-      </c>
-      <c r="E51" s="4" t="s">
-        <v>344</v>
-      </c>
-      <c r="F51" s="4">
-        <v>1964</v>
-      </c>
-      <c r="G51" s="4" t="s">
-        <v>345</v>
-      </c>
-      <c r="H51" s="6"/>
-      <c r="I51" s="6">
-        <v>14</v>
-      </c>
-      <c r="J51" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="K51" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="L51" s="8" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12" ht="33.75" thickBot="1">
-      <c r="A52" s="4" t="s">
-        <v>347</v>
-      </c>
-      <c r="B52" s="4" t="s">
-        <v>341</v>
-      </c>
-      <c r="C52" s="4" t="s">
-        <v>342</v>
-      </c>
-      <c r="D52" s="4" t="s">
-        <v>343</v>
-      </c>
-      <c r="E52" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="F52" s="4">
-        <v>1971</v>
-      </c>
-      <c r="G52" s="4" t="s">
-        <v>349</v>
-      </c>
-      <c r="H52" s="6"/>
-      <c r="I52" s="6">
-        <v>22</v>
-      </c>
-      <c r="J52" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="K52" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="L52" s="8" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12" ht="15.75" thickBot="1">
-      <c r="A53" s="4" t="s">
-        <v>351</v>
-      </c>
-      <c r="B53" s="4" t="s">
-        <v>352</v>
-      </c>
-      <c r="C53" s="4" t="s">
-        <v>352</v>
-      </c>
-      <c r="D53" s="4" t="s">
-        <v>352</v>
-      </c>
-      <c r="E53" s="4" t="s">
-        <v>353</v>
-      </c>
-      <c r="F53" s="4">
-        <v>1943</v>
-      </c>
-      <c r="G53" s="4" t="s">
-        <v>354</v>
-      </c>
-      <c r="H53" s="6"/>
-      <c r="I53" s="6">
-        <v>4</v>
-      </c>
-      <c r="J53" s="6" t="s">
-        <v>355</v>
-      </c>
-      <c r="K53" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="L53" s="6" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12" ht="15.75" thickBot="1">
-      <c r="A54" s="4" t="s">
-        <v>357</v>
-      </c>
-      <c r="B54" s="4" t="s">
-        <v>358</v>
-      </c>
-      <c r="C54" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="D54" s="4" t="s">
-        <v>358</v>
-      </c>
-      <c r="E54" s="4" t="s">
-        <v>359</v>
-      </c>
-      <c r="F54" s="4">
-        <v>1965</v>
-      </c>
-      <c r="G54" s="4" t="s">
-        <v>360</v>
-      </c>
-      <c r="H54" s="6"/>
-      <c r="I54" s="6">
-        <v>28</v>
-      </c>
-      <c r="J54" s="6" t="s">
-        <v>361</v>
-      </c>
-      <c r="K54" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="L54" s="8" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12" ht="15.75" thickBot="1">
-      <c r="A55" s="4" t="s">
-        <v>363</v>
-      </c>
-      <c r="B55" s="4" t="s">
-        <v>364</v>
-      </c>
-      <c r="C55" s="4" t="s">
-        <v>365</v>
-      </c>
-      <c r="D55" s="4" t="s">
-        <v>364</v>
-      </c>
-      <c r="E55" s="4" t="s">
-        <v>366</v>
-      </c>
-      <c r="F55" s="4">
-        <v>1969</v>
-      </c>
-      <c r="G55" s="4" t="s">
-        <v>367</v>
-      </c>
-      <c r="H55" s="6"/>
-      <c r="I55" s="6">
-        <v>6</v>
-      </c>
-      <c r="J55" s="6" t="s">
-        <v>368</v>
-      </c>
-      <c r="K55" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="L55" s="8" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="56" spans="1:12" ht="15.75" thickBot="1">
-      <c r="A56" s="4" t="s">
-        <v>370</v>
-      </c>
-      <c r="B56" s="4" t="s">
-        <v>371</v>
-      </c>
-      <c r="C56" s="4" t="s">
-        <v>372</v>
-      </c>
-      <c r="D56" s="4" t="s">
-        <v>371</v>
-      </c>
-      <c r="E56" s="4" t="s">
-        <v>373</v>
-      </c>
-      <c r="F56" s="4">
-        <v>1956</v>
-      </c>
-      <c r="G56" s="4" t="s">
-        <v>374</v>
-      </c>
-      <c r="H56" s="6"/>
-      <c r="I56" s="6">
-        <v>8</v>
-      </c>
-      <c r="J56" s="6" t="s">
-        <v>375</v>
-      </c>
-      <c r="K56" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="L56" s="8" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="57" spans="1:12" ht="23.25" thickBot="1">
-      <c r="A57" s="14" t="s">
-        <v>376</v>
-      </c>
-      <c r="B57" s="4" t="s">
-        <v>377</v>
-      </c>
-      <c r="C57" s="14" t="s">
-        <v>378</v>
-      </c>
-      <c r="D57" s="6" t="s">
-        <v>377</v>
-      </c>
-      <c r="E57" s="6" t="s">
-        <v>379</v>
-      </c>
-      <c r="F57" s="6">
-        <v>1962</v>
-      </c>
-      <c r="G57" s="6" t="s">
-        <v>380</v>
-      </c>
-      <c r="H57" s="6"/>
-      <c r="I57" s="6">
-        <v>48</v>
-      </c>
-      <c r="J57" s="6" t="s">
-        <v>381</v>
-      </c>
-      <c r="K57" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="L57" s="8" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="58" spans="1:12" ht="23.25" thickBot="1">
-      <c r="A58" s="7" t="s">
-        <v>383</v>
-      </c>
-      <c r="B58" s="4" t="s">
-        <v>377</v>
-      </c>
-      <c r="C58" s="14" t="s">
-        <v>146</v>
-      </c>
-      <c r="D58" s="6" t="s">
-        <v>377</v>
-      </c>
-      <c r="E58" s="6" t="s">
-        <v>384</v>
-      </c>
-      <c r="F58" s="6">
-        <v>1971</v>
-      </c>
-      <c r="G58" s="6" t="s">
-        <v>385</v>
-      </c>
-      <c r="H58" s="6"/>
-      <c r="I58" s="6">
-        <v>42</v>
-      </c>
-      <c r="J58" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="K58" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="L58" s="8" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="59" spans="1:12" ht="33.75" thickBot="1">
-      <c r="A59" s="4" t="s">
-        <v>387</v>
-      </c>
-      <c r="B59" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="C59" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="D59" s="16" t="s">
-        <v>388</v>
-      </c>
-      <c r="E59" s="4" t="s">
-        <v>389</v>
-      </c>
-      <c r="F59" s="4">
-        <v>1974</v>
-      </c>
-      <c r="G59" s="4" t="s">
+      <c r="J59" s="4" t="s">
         <v>390</v>
       </c>
-      <c r="H59" s="6"/>
-      <c r="I59" s="6">
-        <v>10</v>
-      </c>
-      <c r="J59" s="6" t="s">
+      <c r="K59" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L59" s="6" t="s">
         <v>391</v>
       </c>
-      <c r="K59" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="L59" s="8" t="s">
-        <v>392</v>
-      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A3 A9:F9 C2 A8 C8:G8 A14 E14:G14 C14 E2:G2 C3:F3 A4:G7 A10:G13 A15:G59">
-    <cfRule type="expression" priority="7">
-      <formula>$N2="Missing"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B2">
-    <cfRule type="expression" priority="6">
-      <formula>$Q2="Missing"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B3">
-    <cfRule type="expression" priority="5">
-      <formula>$Q3="Missing"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B8">
-    <cfRule type="expression" priority="4">
-      <formula>$Q8="Missing"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D14">
-    <cfRule type="expression" priority="3">
-      <formula>$Q14="Missing"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B14">
-    <cfRule type="expression" priority="2">
-      <formula>$Q14="Missing"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D2">
-    <cfRule type="expression" priority="1">
-      <formula>$N2="Missing"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>